--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,14 +553,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 10/10  ·  전일분: RISE, TIGER 기술이전, TIGER 코스닥, MIDAS  ·  전부 반영 완료</t>
+          <t>캡처 10/10  ·  전부 반영 완료  ·  검증필요 1건</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,380억   ·   현금 16억(0.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 5종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,331억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>840524451</v>
+        <v>838836836</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>-34</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2086022526</v>
+        <v>-2081834186</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1597285296</v>
+        <v>1594078249</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>-33</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-866071852</v>
+        <v>-864332943</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2265900136</v>
+        <v>2261350637</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>-15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-627480038</v>
+        <v>-626220176</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>862187452</v>
+        <v>860456342</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>-11</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1624774898</v>
+        <v>-1621512657</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>865524052</v>
+        <v>863786243</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,140억   ·   현금 61억(2.0%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 8종목  /  매도 16종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 8종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -949,7 +949,7 @@
         <v>141</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>3763134620</v>
+        <v>3763135040</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>-118</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1489100889</v>
+        <v>-1489101055</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>104</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>4730325248</v>
+        <v>4730325776</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>-113</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2472750566</v>
+        <v>-2472750842</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>65</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1544546135</v>
+        <v>1544546308</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>-58</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1252069107</v>
+        <v>-1252069247</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>39</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1610516580</v>
+        <v>1610516760</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>-43</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-5183929114</v>
+        <v>-5183929693</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>922888131</v>
+        <v>922888234</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>-38</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-2107939643</v>
+        <v>-2107939879</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>9446903296</v>
+        <v>9446904352</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>-33</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1208572110</v>
+        <v>-1208572245</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>939535130</v>
+        <v>939535235</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>-32</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-3094838169</v>
+        <v>-3094838515</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>6</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>151595089</v>
+        <v>151595106</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>-26</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-178015487</v>
+        <v>-178015507</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>-25</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-289308728</v>
+        <v>-289308761</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>-24</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-480077964</v>
+        <v>-480078018</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>-22</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1062078521</v>
+        <v>-1062078640</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>-22</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2829452789</v>
+        <v>-2829453105</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>-18</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-153882709</v>
+        <v>-153882726</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1358878399</v>
+        <v>-1358878551</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-27934738</v>
+        <v>-27934741</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>-4</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-58425596</v>
+        <v>-58425602</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,218억   ·   현금 45억(2.1%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 14종목  /  매도 16종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,181억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 14종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1607,14 +1607,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>씨어스 ※</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
         <v>201</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>3144040285</v>
+        <v>3144043715</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>-129</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-4776351395</v>
+        <v>-4776356605</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>200</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1471799197</v>
+        <v>1471800803</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>-120</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1090583405</v>
+        <v>-1090584595</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>150</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>3460048113</v>
+        <v>3460051887</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>-118</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1084867808</v>
+        <v>-1084868992</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1739,14 +1739,16 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>펌텍코리아  (신규)</t>
+          <t>펌텍코리아  (신규) ※검증필요</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>5520236989</v>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>검증필요</t>
+        </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1767,7 +1769,7 @@
         <v>-110</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2112658848</v>
+        <v>-2112661152</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1790,7 +1792,7 @@
         <v>100</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2633398564</v>
+        <v>2633401436</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1811,7 +1813,7 @@
         <v>-100</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1696199075</v>
+        <v>-1696200925</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1834,7 +1836,7 @@
         <v>100</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1709399068</v>
+        <v>1709400932</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1855,7 +1857,7 @@
         <v>-55</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2824138460</v>
+        <v>-2824141540</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1871,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>739199597</v>
+        <v>2029501107</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>0.00%→0.95%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1899,7 +1901,7 @@
         <v>-49</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2121502843</v>
+        <v>-2121505157</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1915,23 +1917,23 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2029498893</v>
+        <v>2306701258</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.95%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -1943,7 +1945,7 @@
         <v>-33</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2208490795</v>
+        <v>-2208493205</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1959,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2306698742</v>
+        <v>739200403</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -1987,7 +1989,7 @@
         <v>-27</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1915648955</v>
+        <v>-1915651045</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2010,7 +2012,7 @@
         <v>35</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>696464620</v>
+        <v>696465380</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2031,7 +2033,7 @@
         <v>-25</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1583999136</v>
+        <v>-1584000864</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2054,7 +2056,7 @@
         <v>30</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2366098709</v>
+        <v>2366101291</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2075,7 +2077,7 @@
         <v>-24</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1080287411</v>
+        <v>-1080288589</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2098,7 +2100,7 @@
         <v>28</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>677291631</v>
+        <v>677292369</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2112,90 +2114,90 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1454639207</v>
+        <v>-2374681295</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.48%→0.85%</t>
+          <t>4.52%→3.34%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>45→25</t>
+          <t>80→60</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2370718707</v>
+        <v>2713921480</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>1.46%→2.78%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>29→45</t>
+          <t>19→35</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-2374678705</v>
+        <v>-1454640793</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>4.52%→3.34%</t>
+          <t>1.48%→0.85%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>80→60</t>
+          <t>45→25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2713918520</v>
+        <v>2370721293</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.46%→2.78%</t>
+          <t>2.03%→3.12%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>19→35</t>
+          <t>29→45</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2207,7 +2209,7 @@
         <v>-19</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1423289224</v>
+        <v>-1423290776</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2235,7 +2237,7 @@
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-566675691</v>
+        <v>-566676309</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2263,7 +2265,7 @@
         <v>-18</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-4799517382</v>
+        <v>-4799522618</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2279,7 +2281,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,131억   ·   현금 1억(0.0%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,148억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -2375,7 +2377,7 @@
         <v>8</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>129926413</v>
+        <v>129926451</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2396,7 +2398,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 248억   ·   현금 2억(0.8%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 2종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2492,11 +2494,11 @@
         <v>146</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>76153576</v>
+        <v>75219153</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>6.92%→7.21%</t>
+          <t>6.96%→7.26%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2513,11 +2515,11 @@
         <v>-8</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-55654383</v>
+        <v>-61183962</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.19%</t>
+          <t>1.59%→1.33%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2536,11 +2538,11 @@
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>37055988</v>
+        <v>36710377</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>1.81%→1.96%</t>
+          <t>1.83%→1.98%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2557,7 +2559,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 429억   ·   현금 -2억(-0.4%)      ※전일분  PDF 2026-10-23  vs  2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 425억   ·   현금 -2억(-0.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 2종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2572,98 +2574,190 @@
       <c r="K63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      ※전일분  PDF 2026-10-23  vs  2026-10-22      매수 0종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>521413017</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>2.65%→3.92%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>119→173</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (편출)</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-179</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-345677519</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.80%→0.00%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>179→0</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>삼성바이오로직스</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>1838363355</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>2.52%→7.05%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>7→18</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>큐라클  (편출)</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-99</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-100219645</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>0.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>99→0</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A68" s="17" t="n"/>
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="17" t="n"/>
+      <c r="D68" s="17" t="n"/>
+      <c r="E68" s="17" t="n"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-412064255</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>5.45%→4.45%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>297→244</t>
         </is>
       </c>
     </row>
@@ -2675,23 +2769,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-4</v>
+        <v>-48</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-73311907</v>
+        <v>-491932627</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.20%</t>
+          <t>4.56%→3.46%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>192→144</t>
         </is>
       </c>
     </row>
@@ -2703,906 +2797,668 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-3</v>
+        <v>-40</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-432639996</v>
+        <v>-98723965</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>7.70%→5.22%</t>
+          <t>4.37%→4.39%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>40→37</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억   ·   현금 3억(0.3%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 6종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
+          <t>798→758</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="n"/>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-153552246</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>5.25%→5.03%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>464→433</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="n"/>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>휴젤  (편출)</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-432835048</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.00%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>21→0</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="17" t="n"/>
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="17" t="n"/>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-327635885</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>3.64%→2.69%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>54→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 58억(5.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 6종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="J78" s="4" t="n"/>
+      <c r="K78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="8" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="8" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E74" s="9" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H74" s="9" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr">
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>샘씨엔에스</t>
         </is>
       </c>
-      <c r="B75" s="11" t="n">
+      <c r="B81" s="11" t="n">
         <v>196</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>507018498</v>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="C81" s="11" t="n">
+        <v>513090639</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>5.06%→5.79%</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>1,689→1,885</t>
         </is>
       </c>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>디케이티</t>
         </is>
       </c>
-      <c r="H75" s="15" t="n">
+      <c r="H81" s="15" t="n">
         <v>-191</v>
       </c>
-      <c r="I75" s="15" t="n">
-        <v>-826132003</v>
-      </c>
-      <c r="J75" s="16" t="inlineStr">
+      <c r="I81" s="15" t="n">
+        <v>-836025902</v>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
         <is>
           <t>5.33%→4.95%</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K81" s="13" t="inlineStr">
         <is>
           <t>1,155→964</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>아스플로</t>
         </is>
       </c>
-      <c r="B76" s="11" t="n">
+      <c r="B82" s="11" t="n">
         <v>185</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>980915898</v>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="C82" s="11" t="n">
+        <v>992663515</v>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>2.35%→3.61%</t>
         </is>
       </c>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>389→574</t>
         </is>
       </c>
-      <c r="G76" s="14" t="inlineStr">
+      <c r="G82" s="14" t="inlineStr">
         <is>
           <t>코세스</t>
         </is>
       </c>
-      <c r="H76" s="15" t="n">
+      <c r="H82" s="15" t="n">
         <v>-189</v>
       </c>
-      <c r="I76" s="15" t="n">
-        <v>-1259363248</v>
-      </c>
-      <c r="J76" s="16" t="inlineStr">
+      <c r="I82" s="15" t="n">
+        <v>-1274445598</v>
+      </c>
+      <c r="J82" s="16" t="inlineStr">
         <is>
           <t>4.27%→2.98%</t>
         </is>
       </c>
-      <c r="K76" s="13" t="inlineStr">
+      <c r="K82" s="13" t="inlineStr">
         <is>
           <t>566→377</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>뉴파워프라즈마</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
+      <c r="B83" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>139052500</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="C83" s="11" t="n">
+        <v>140717817</v>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>3.65%→3.87%</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>1,367→1,428</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>리노공업</t>
         </is>
       </c>
-      <c r="H77" s="15" t="n">
+      <c r="H83" s="15" t="n">
         <v>-62</v>
       </c>
-      <c r="I77" s="15" t="n">
-        <v>-637806171</v>
-      </c>
-      <c r="J77" s="16" t="inlineStr">
+      <c r="I83" s="15" t="n">
+        <v>-645444647</v>
+      </c>
+      <c r="J83" s="16" t="inlineStr">
         <is>
           <t>4.50%→3.57%</t>
         </is>
       </c>
-      <c r="K77" s="13" t="inlineStr">
+      <c r="K83" s="13" t="inlineStr">
         <is>
           <t>354→292</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n">
+      <c r="B84" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>477803528</v>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="C84" s="11" t="n">
+        <v>483525786</v>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>2.39%→2.97%</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>216→267</t>
         </is>
       </c>
-      <c r="G78" s="17" t="n"/>
-      <c r="H78" s="17" t="n"/>
-      <c r="I78" s="17" t="n"/>
-      <c r="J78" s="17" t="n"/>
-      <c r="K78" s="17" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>미코</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="C79" s="11" t="n">
-        <v>153372745</v>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>5.36%→5.54%</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>1,206→1,247</t>
-        </is>
-      </c>
-      <c r="G79" s="17" t="n"/>
-      <c r="H79" s="17" t="n"/>
-      <c r="I79" s="17" t="n"/>
-      <c r="J79" s="17" t="n"/>
-      <c r="K79" s="17" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>심텍</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C80" s="11" t="n">
-        <v>322226384</v>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>5.37%→5.49%</t>
-        </is>
-      </c>
-      <c r="E80" s="13" t="inlineStr">
-        <is>
-          <t>227→244</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="n"/>
-      <c r="H80" s="17" t="n"/>
-      <c r="I80" s="17" t="n"/>
-      <c r="J80" s="17" t="n"/>
-      <c r="K80" s="17" t="n"/>
-    </row>
-    <row r="82" ht="19" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      ※전일분  PDF 2026-10-23  vs  2026-10-22      매수 4종목  /  매도 5종목</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="6" t="n"/>
-      <c r="D83" s="6" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="8" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="G84" s="17" t="n"/>
+      <c r="H84" s="17" t="n"/>
+      <c r="I84" s="17" t="n"/>
+      <c r="J84" s="17" t="n"/>
+      <c r="K84" s="17" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>파인엠텍  (신규)</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>333963630</v>
+        <v>155209563</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.13%</t>
+          <t>5.36%→5.54%</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>0→77</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>동국산업</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>-69</v>
-      </c>
-      <c r="I85" s="15" t="n">
-        <v>-118848015</v>
-      </c>
-      <c r="J85" s="16" t="inlineStr">
-        <is>
-          <t>1.37%→0.98%</t>
-        </is>
-      </c>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>237→168</t>
-        </is>
-      </c>
+          <t>1,206→1,247</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="n"/>
+      <c r="H85" s="17" t="n"/>
+      <c r="I85" s="17" t="n"/>
+      <c r="J85" s="17" t="n"/>
+      <c r="K85" s="17" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>313513200</v>
+        <v>326085423</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>5.37%→5.49%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t>에이팩트</t>
-        </is>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>-63</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>-232972740</v>
-      </c>
-      <c r="J86" s="16" t="inlineStr">
-        <is>
-          <t>2.97%→2.21%</t>
-        </is>
-      </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>240→177</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>지엔씨에너지</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C87" s="11" t="n">
-        <v>127327200</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>0.55%→0.98%</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>9→16</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>HLB이노베이션</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I87" s="15" t="n">
-        <v>-81750240</v>
-      </c>
-      <c r="J87" s="16" t="inlineStr">
-        <is>
-          <t>0.91%→0.64%</t>
-        </is>
-      </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>40→28</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>한라IMS</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
+          <t>227→244</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="n"/>
+      <c r="H86" s="17" t="n"/>
+      <c r="I86" s="17" t="n"/>
+      <c r="J86" s="17" t="n"/>
+      <c r="K86" s="17" t="n"/>
+    </row>
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억   ·   현금 4억(1.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 3종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
+      <c r="K88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>18815940</v>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>0.23%→0.30%</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="inlineStr">
-        <is>
-          <t>11→14</t>
-        </is>
-      </c>
-      <c r="G88" s="14" t="inlineStr">
-        <is>
-          <t>오이솔루션</t>
-        </is>
-      </c>
-      <c r="H88" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I88" s="15" t="n">
-        <v>-77177100</v>
-      </c>
-      <c r="J88" s="16" t="inlineStr">
-        <is>
-          <t>1.03%→0.78%</t>
-        </is>
-      </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>28→21</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="17" t="n"/>
-      <c r="B89" s="17" t="n"/>
-      <c r="C89" s="17" t="n"/>
-      <c r="D89" s="17" t="n"/>
-      <c r="E89" s="17" t="n"/>
-      <c r="G89" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="H89" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I89" s="15" t="n">
-        <v>-201115200</v>
-      </c>
-      <c r="J89" s="16" t="inlineStr">
-        <is>
-          <t>1.68%→1.02%</t>
-        </is>
-      </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>10→6</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      ※전일분  PDF 2026-10-23  vs  2026-10-22      매수 4종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
+      <c r="C91" s="11" t="n">
+        <v>8772002</v>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>2.85%→2.69%</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>269→272</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="n"/>
+      <c r="H91" s="17" t="n"/>
+      <c r="I91" s="17" t="n"/>
+      <c r="J91" s="17" t="n"/>
+      <c r="K91" s="17" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="n"/>
-      <c r="J92" s="8" t="n"/>
-      <c r="K92" s="8" t="n"/>
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>11742753</v>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.04%</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>0→3</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="n"/>
+      <c r="H92" s="17" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K93" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>큐리언트  (신규)</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="n">
-        <v>176</v>
-      </c>
-      <c r="C94" s="11" t="n">
-        <v>28441600</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.51%</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>0→176</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="H94" s="15" t="n">
-        <v>-98</v>
-      </c>
-      <c r="I94" s="15" t="n">
-        <v>-27283200</v>
-      </c>
-      <c r="J94" s="16" t="inlineStr">
-        <is>
-          <t>3.44%→2.93%</t>
-        </is>
-      </c>
-      <c r="K94" s="13" t="inlineStr">
-        <is>
-          <t>683→585</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="C95" s="11" t="n">
-        <v>21974400</v>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>3.18%→3.57%</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr">
-        <is>
-          <t>449→505</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I95" s="15" t="n">
-        <v>-24371200</v>
-      </c>
-      <c r="J95" s="16" t="inlineStr">
-        <is>
-          <t>4.36%→3.90%</t>
-        </is>
-      </c>
-      <c r="K95" s="13" t="inlineStr">
-        <is>
-          <t>277→249</t>
-        </is>
-      </c>
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>4277626</v>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.01%</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>0→3</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="n"/>
+      <c r="H93" s="17" t="n"/>
+      <c r="I93" s="17" t="n"/>
+      <c r="J93" s="17" t="n"/>
+      <c r="K93" s="17" t="n"/>
+    </row>
+    <row r="95" ht="19" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C96" s="11" t="n">
-        <v>9792000</v>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>2.61%→2.78%</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="inlineStr">
-        <is>
-          <t>177→189</t>
-        </is>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>-19</v>
-      </c>
-      <c r="I96" s="15" t="n">
-        <v>-25612000</v>
-      </c>
-      <c r="J96" s="16" t="inlineStr">
-        <is>
-          <t>4.92%→4.44%</t>
-        </is>
-      </c>
-      <c r="K96" s="13" t="inlineStr">
-        <is>
-          <t>202→183</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>이오테크닉스</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C97" s="11" t="n">
-        <v>36080000</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>5.99%→6.62%</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="inlineStr">
-        <is>
-          <t>101→112</t>
-        </is>
-      </c>
-      <c r="G97" s="17" t="n"/>
-      <c r="H97" s="17" t="n"/>
-      <c r="I97" s="17" t="n"/>
-      <c r="J97" s="17" t="n"/>
-      <c r="K97" s="17" t="n"/>
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A82:K82"/>
-    <mergeCell ref="G67:K67"/>
+  <mergeCells count="30">
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="A78:K78"/>
     <mergeCell ref="G13:K13"/>
     <mergeCell ref="G53:K53"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="G92:K92"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A12:K12"/>
-    <mergeCell ref="G83:K83"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A57:K57"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="G33:K33"/>
     <mergeCell ref="G58:K58"/>
+    <mergeCell ref="G89:K89"/>
+    <mergeCell ref="A95:K95"/>
     <mergeCell ref="A32:K32"/>
-    <mergeCell ref="G73:K73"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="G79:K79"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G64:K64"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A96:K96"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A52:K52"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1785,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2633401436</v>
+        <v>1709400932</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>1.73%→3.08%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>150→250</t>
+          <t>0→100</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1829,23 +1829,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1709400932</v>
+        <v>2633401436</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>1.73%→3.08%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>150→250</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2230,23 +2230,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-566676309</v>
+        <v>-4799522618</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.21%</t>
+          <t>3.72%→1.50%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>100→82</t>
+          <t>30→12</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-4799522618</v>
+        <v>-566676309</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.50%</t>
+          <t>1.46%→1.21%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>30→12</t>
+          <t>100→82</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 425억   ·   현금 -2억(-0.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 2종목  /  매도 8종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 425억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 2종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2904,7 +2904,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 58억(5.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
@@ -3233,7 +3233,7 @@
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억   ·   현금 4억(1.4%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 3종목  /  매도 0종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 3종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
@@ -3322,23 +3322,23 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8772002</v>
+        <v>4277626</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>2.85%→2.69%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>269→272</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G91" s="17" t="n"/>
@@ -3350,23 +3350,23 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>11742753</v>
+        <v>8772002</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>2.85%→2.69%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>269→272</t>
         </is>
       </c>
       <c r="G92" s="17" t="n"/>
@@ -3378,18 +3378,18 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
@@ -3406,7 +3406,7 @@
     <row r="95" ht="19" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억      당일 2026-10-26  vs  전영업일 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B95" s="4" t="n"/>

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1785,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1709400932</v>
+        <v>2633401436</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>1.73%→3.08%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>150→250</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1829,23 +1829,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2633401436</v>
+        <v>1709400932</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1.73%→3.08%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>150→250</t>
+          <t>0→100</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1873,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2029501107</v>
+        <v>739200403</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.95%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1917,23 +1917,23 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2306701258</v>
+        <v>2029501107</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>0.00%→0.95%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>739200403</v>
+        <v>2306701258</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2114,90 +2114,90 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2374681295</v>
+        <v>-1454640793</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>4.52%→3.34%</t>
+          <t>1.48%→0.85%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>80→60</t>
+          <t>45→25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2713921480</v>
+        <v>2370721293</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.46%→2.78%</t>
+          <t>2.03%→3.12%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>19→35</t>
+          <t>29→45</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1454640793</v>
+        <v>-2374681295</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.48%→0.85%</t>
+          <t>4.52%→3.34%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>45→25</t>
+          <t>80→60</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2370721293</v>
+        <v>2713921480</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>1.46%→2.78%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>29→45</t>
+          <t>19→35</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3322,18 +3322,18 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3378,18 +3378,18 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>11742753</v>
+        <v>4277626</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1873,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>739200403</v>
+        <v>2306701258</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2306701258</v>
+        <v>739200403</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2137,23 +2137,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2370721293</v>
+        <v>2713921480</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>1.46%→2.78%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>29→45</t>
+          <t>19→35</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2181,23 +2181,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2713921480</v>
+        <v>2370721293</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.46%→2.78%</t>
+          <t>2.03%→3.12%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>19→35</t>
+          <t>29→45</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2230,23 +2230,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4799522618</v>
+        <v>-566676309</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.50%</t>
+          <t>1.46%→1.21%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>30→12</t>
+          <t>100→82</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-566676309</v>
+        <v>-4799522618</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.21%</t>
+          <t>3.72%→1.50%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>100→82</t>
+          <t>30→12</t>
         </is>
       </c>
     </row>
@@ -3322,23 +3322,23 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>11742753</v>
+        <v>8772002</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>2.85%→2.69%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>269→272</t>
         </is>
       </c>
       <c r="G91" s="17" t="n"/>
@@ -3350,23 +3350,23 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>8772002</v>
+        <v>4277626</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>2.85%→2.69%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>269→272</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G92" s="17" t="n"/>
@@ -3378,18 +3378,18 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1355,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1062078640</v>
+        <v>-2829453105</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>7.23%→6.97%</t>
+          <t>3.60%→2.49%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2829453105</v>
+        <v>-1062078640</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.60%→2.49%</t>
+          <t>7.23%→6.97%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1873,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2306701258</v>
+        <v>2029501107</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>0.00%→0.95%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1917,23 +1917,23 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2029501107</v>
+        <v>739200403</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.95%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>739200403</v>
+        <v>2306701258</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2114,23 +2114,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1454640793</v>
+        <v>-2374681295</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.48%→0.85%</t>
+          <t>4.52%→3.34%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>45→25</t>
+          <t>80→60</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-2374681295</v>
+        <v>-1454640793</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>4.52%→3.34%</t>
+          <t>1.48%→0.85%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>80→60</t>
+          <t>45→25</t>
         </is>
       </c>
     </row>
@@ -2230,23 +2230,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-566676309</v>
+        <v>-4799522618</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.21%</t>
+          <t>3.72%→1.50%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>100→82</t>
+          <t>30→12</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-4799522618</v>
+        <v>-566676309</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.50%</t>
+          <t>1.46%→1.21%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>30→12</t>
+          <t>100→82</t>
         </is>
       </c>
     </row>
@@ -3350,18 +3350,18 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -3378,18 +3378,18 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>11742753</v>
+        <v>4277626</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1355,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-2829453105</v>
+        <v>-1062078640</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>3.60%→2.49%</t>
+          <t>7.23%→6.97%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1062078640</v>
+        <v>-2829453105</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>7.23%→6.97%</t>
+          <t>3.60%→2.49%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -1873,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2029501107</v>
+        <v>739200403</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.95%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1917,23 +1917,23 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>739200403</v>
+        <v>2306701258</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2306701258</v>
+        <v>2029501107</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>0.00%→0.95%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2137,23 +2137,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2713921480</v>
+        <v>2370721293</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.46%→2.78%</t>
+          <t>2.03%→3.12%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>19→35</t>
+          <t>29→45</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2181,23 +2181,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2370721293</v>
+        <v>2713921480</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>1.46%→2.78%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>29→45</t>
+          <t>19→35</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3322,23 +3322,23 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8772002</v>
+        <v>4277626</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>2.85%→2.69%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>269→272</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G91" s="17" t="n"/>
@@ -3350,23 +3350,23 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>11742753</v>
+        <v>8772002</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>2.85%→2.69%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>269→272</t>
         </is>
       </c>
       <c r="G92" s="17" t="n"/>
@@ -3378,18 +3378,18 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1785,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2633401436</v>
+        <v>1709400932</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>1.73%→3.08%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>150→250</t>
+          <t>0→100</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1829,23 +1829,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1709400932</v>
+        <v>2633401436</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>1.73%→3.08%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>150→250</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1917,23 +1917,23 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2306701258</v>
+        <v>2029501107</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>0.00%→0.95%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (재편입·10/21까지 50주)</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2029501107</v>
+        <v>2306701258</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.95%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2114,90 +2114,90 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2374681295</v>
+        <v>-1454640793</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>4.52%→3.34%</t>
+          <t>1.48%→0.85%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>80→60</t>
+          <t>45→25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2370721293</v>
+        <v>2713921480</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>1.46%→2.78%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>29→45</t>
+          <t>19→35</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1454640793</v>
+        <v>-2374681295</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.48%→0.85%</t>
+          <t>4.52%→3.34%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>45→25</t>
+          <t>80→60</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2713921480</v>
+        <v>2370721293</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.46%→2.78%</t>
+          <t>2.03%→3.12%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>19→35</t>
+          <t>29→45</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3322,18 +3322,18 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>4277626</v>
+        <v>11742753</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3350,23 +3350,23 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>8772002</v>
+        <v>4277626</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>2.85%→2.69%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>269→272</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G92" s="17" t="n"/>
@@ -3378,23 +3378,23 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>11742753</v>
+        <v>8772002</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>2.85%→2.69%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>269→272</t>
         </is>
       </c>
       <c r="G93" s="17" t="n"/>

--- a/reports/pdf_change_20261026.xlsx
+++ b/reports/pdf_change_20261026.xlsx
@@ -1785,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1709400932</v>
+        <v>2633401436</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>1.73%→3.08%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>150→250</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -1829,23 +1829,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2633401436</v>
+        <v>1709400932</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1.73%→3.08%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>150→250</t>
+          <t>0→100</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1873,23 +1873,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>739200403</v>
+        <v>2306701258</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.77%</t>
+          <t>4.93%→6.05%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>350→400</t>
+          <t>230→280</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -1961,23 +1961,23 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2306701258</v>
+        <v>739200403</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>4.93%→6.05%</t>
+          <t>2.38%→2.77%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>230→280</t>
+          <t>350→400</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2230,23 +2230,23 @@
       <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4799522618</v>
+        <v>-566676309</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.50%</t>
+          <t>1.46%→1.21%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>30→12</t>
+          <t>100→82</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2258,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-18</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-566676309</v>
+        <v>-4799522618</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.21%</t>
+          <t>3.72%→1.50%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>100→82</t>
+          <t>30→12</t>
         </is>
       </c>
     </row>
@@ -3322,18 +3322,18 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
+          <t>피엠티  (재편입·10/21까지 53주)</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>11742753</v>
+        <v>4277626</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3350,23 +3350,23 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>4277626</v>
+        <v>8772002</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>2.85%→2.69%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>269→272</t>
         </is>
       </c>
       <c r="G92" s="17" t="n"/>
@@ -3378,23 +3378,23 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>8772002</v>
+        <v>11742753</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>2.85%→2.69%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>269→272</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G93" s="17" t="n"/>
